--- a/data/trans_orig/P37C2_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P37C2_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la creencia de que las vacunas son seguras en 2023</t>
+          <t>Población según la creencia de que las vacunas son seguras en 2023 (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1669</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>334</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11163</t>
+          <t>10202</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>322</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>11712</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3207</t>
+          <t>3024</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13279</t>
+          <t>13264</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>821</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6114</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5283</t>
+          <t>4893</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15821</t>
+          <t>16572</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22786</t>
+          <t>22936</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>46118</t>
+          <t>46372</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15697</t>
+          <t>15859</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30692</t>
+          <t>29575</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>41534</t>
+          <t>43653</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>71095</t>
+          <t>69785</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>100347</t>
+          <t>101398</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>138960</t>
+          <t>139198</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>104514</t>
+          <t>103091</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>133883</t>
+          <t>133611</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>215583</t>
+          <t>212452</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>262106</t>
+          <t>262441</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,2%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>448316</t>
+          <t>448311</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>491660</t>
+          <t>491681</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>508321</t>
+          <t>509525</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>540378</t>
+          <t>542235</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>965875</t>
+          <t>967156</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1020993</t>
+          <t>1022610</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>78,71%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13792</t>
+          <t>14986</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>596</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>5774</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2984</t>
+          <t>2526</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15984</t>
+          <t>17621</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>4745</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19119</t>
+          <t>18935</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3086</t>
+          <t>3400</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12839</t>
+          <t>12875</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10732</t>
+          <t>10521</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>27585</t>
+          <t>28174</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25942</t>
+          <t>25403</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>77414</t>
+          <t>76369</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25144</t>
+          <t>26414</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>45553</t>
+          <t>45928</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>63462</t>
+          <t>60115</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>114594</t>
+          <t>114278</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>104514</t>
+          <t>113620</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>278153</t>
+          <t>272008</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>191370</t>
+          <t>189824</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>234515</t>
+          <t>232957</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>295943</t>
+          <t>274913</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>489906</t>
+          <t>487932</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,82%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>817140</t>
+          <t>822973</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1045135</t>
+          <t>1033638</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>673116</t>
+          <t>673694</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>719496</t>
+          <t>720998</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1518045</t>
+          <t>1516841</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1758595</t>
+          <t>1773374</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>82,93%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>883</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9408</t>
+          <t>10889</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,77 +2109,77 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>2503</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>10324</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,04%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>5827</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>1969</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>13215</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>0,12%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2503</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>410</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>9099</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,04%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>5827</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>1637</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>13156</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2443</t>
+          <t>2361</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11937</t>
+          <t>11632</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>1530</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10740</t>
+          <t>10462</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>4796</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18780</t>
+          <t>18990</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>32677</t>
+          <t>32246</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>70059</t>
+          <t>66950</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14534</t>
+          <t>14373</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>47615</t>
+          <t>46665</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>49190</t>
+          <t>48370</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>100773</t>
+          <t>101498</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>180450</t>
+          <t>180313</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>236518</t>
+          <t>238177</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>72989</t>
+          <t>68832</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>205625</t>
+          <t>204957</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>232458</t>
+          <t>233360</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>425166</t>
+          <t>424880</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,04%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>406995</t>
+          <t>408118</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>468291</t>
+          <t>469311</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>674275</t>
+          <t>676300</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>834689</t>
+          <t>843338</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1101190</t>
+          <t>1101195</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1335373</t>
+          <t>1336546</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,91%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>973</t>
+          <t>860</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7949</t>
+          <t>8036</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1858</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11387</t>
+          <t>12062</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4010</t>
+          <t>3844</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15385</t>
+          <t>15796</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7467</t>
+          <t>7743</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22790</t>
+          <t>24559</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2567</t>
+          <t>2749</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>12227</t>
+          <t>12609</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>12651</t>
+          <t>12423</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>32090</t>
+          <t>31316</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>36961</t>
+          <t>36605</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>66563</t>
+          <t>67777</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>48988</t>
+          <t>49707</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>87669</t>
+          <t>88194</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>95826</t>
+          <t>94588</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>144440</t>
+          <t>142827</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>127611</t>
+          <t>130201</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>173938</t>
+          <t>178609</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>188317</t>
+          <t>187112</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>420975</t>
+          <t>444823</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>334197</t>
+          <t>336261</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>596953</t>
+          <t>599651</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,93%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>674331</t>
+          <t>670846</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>727712</t>
+          <t>726703</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>595629</t>
+          <t>603841</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>813768</t>
+          <t>817199</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1284531</t>
+          <t>1282205</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1521417</t>
+          <t>1522311</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>75,98%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5828</t>
+          <t>6292</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>22148</t>
+          <t>22745</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,47 +3473,47 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>11948</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>6149</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>22130</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
           <t>0,17%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>11948</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>6239</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>21095</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>15508</t>
+          <t>14807</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>36024</t>
+          <t>36592</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>25343</t>
+          <t>26297</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>50611</t>
+          <t>52037</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>13605</t>
+          <t>13296</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>30225</t>
+          <t>30634</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>42682</t>
+          <t>43826</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>71987</t>
+          <t>73593</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>145616</t>
+          <t>145680</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>222411</t>
+          <t>220376</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>123048</t>
+          <t>123261</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>180560</t>
+          <t>184498</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>289007</t>
+          <t>285418</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>389005</t>
+          <t>382375</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>541800</t>
+          <t>544855</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>763313</t>
+          <t>767920</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>624402</t>
+          <t>633279</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>910616</t>
+          <t>914965</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1254981</t>
+          <t>1242645</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1619107</t>
+          <t>1582515</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,37%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2418497</t>
+          <t>2417162</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2704114</t>
+          <t>2711381</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2563167</t>
+          <t>2572038</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2857237</t>
+          <t>2855380</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5046842</t>
+          <t>5079816</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5461346</t>
+          <t>5479821</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>77,48%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P37C2_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P37C2_2023-Habitat-trans_orig.xlsx
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2579</t>
+          <t>3235</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>545</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10202</t>
+          <t>11810</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2579</t>
+          <t>3235</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>539</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11712</t>
+          <t>10482</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6748</t>
+          <t>7563</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3024</t>
+          <t>3446</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13264</t>
+          <t>13731</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2537</t>
+          <t>2641</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>956</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>6354</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>9286</t>
+          <t>10204</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4893</t>
+          <t>5490</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16572</t>
+          <t>17292</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>32666</t>
+          <t>42063</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22936</t>
+          <t>30336</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>46372</t>
+          <t>59460</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>21863</t>
+          <t>25501</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15859</t>
+          <t>18092</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29575</t>
+          <t>34089</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>54529</t>
+          <t>67564</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>43653</t>
+          <t>53908</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>69785</t>
+          <t>89002</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>119482</t>
+          <t>131926</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>101398</t>
+          <t>112115</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>139198</t>
+          <t>153090</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>118456</t>
+          <t>127941</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>103091</t>
+          <t>113304</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>133611</t>
+          <t>145987</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>237937</t>
+          <t>259867</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>212452</t>
+          <t>232633</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>262441</t>
+          <t>285218</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,23%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>469482</t>
+          <t>500787</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>448311</t>
+          <t>474723</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>491681</t>
+          <t>522758</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>525332</t>
+          <t>568385</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>509525</t>
+          <t>549862</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>542235</t>
+          <t>583964</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>994814</t>
+          <t>1069171</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>967156</t>
+          <t>1034783</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1022610</t>
+          <t>1099712</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>77,99%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>628378</t>
+          <t>682339</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>628378</t>
+          <t>682339</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>628378</t>
+          <t>682339</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>670768</t>
+          <t>727702</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>670768</t>
+          <t>727702</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>670768</t>
+          <t>727702</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1299145</t>
+          <t>1410040</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1299145</t>
+          <t>1410040</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1299145</t>
+          <t>1410040</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5484</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14986</t>
+          <t>11761</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,22 +1442,22 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2138</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>674</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5774</t>
+          <t>6202</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>7495</t>
+          <t>7055</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2526</t>
+          <t>3048</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17621</t>
+          <t>15063</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10515</t>
+          <t>11011</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4745</t>
+          <t>6042</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18935</t>
+          <t>19465</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7105</t>
+          <t>7610</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3400</t>
+          <t>3517</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12875</t>
+          <t>13396</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>17619</t>
+          <t>18621</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10521</t>
+          <t>12043</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28174</t>
+          <t>27398</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>55161</t>
+          <t>62111</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25403</t>
+          <t>46383</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>76369</t>
+          <t>81320</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,27 +1668,27 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>34736</t>
+          <t>39518</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>26414</t>
+          <t>29687</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>45928</t>
+          <t>51404</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>89897</t>
+          <t>101629</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>60115</t>
+          <t>83046</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>114278</t>
+          <t>123609</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>208569</t>
+          <t>232191</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>113620</t>
+          <t>202272</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>272008</t>
+          <t>263515</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>211186</t>
+          <t>232782</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>189824</t>
+          <t>212719</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>232957</t>
+          <t>256642</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>419755</t>
+          <t>464973</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>274913</t>
+          <t>427856</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>487932</t>
+          <t>503661</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>23,93%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>905216</t>
+          <t>728096</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>822973</t>
+          <t>694895</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1033638</t>
+          <t>759708</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>698530</t>
+          <t>784024</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>673694</t>
+          <t>758063</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>720998</t>
+          <t>805896</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1603746</t>
+          <t>1512121</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1516841</t>
+          <t>1468066</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1773374</t>
+          <t>1549958</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>73,65%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1184944</t>
+          <t>1038326</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1184944</t>
+          <t>1038326</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1184944</t>
+          <t>1038326</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>953568</t>
+          <t>1066072</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>953568</t>
+          <t>1066072</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>953568</t>
+          <t>1066072</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2138512</t>
+          <t>2104399</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2138512</t>
+          <t>2104399</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2138512</t>
+          <t>2104399</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>883</t>
+          <t>833</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10889</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2503</t>
+          <t>3562</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10324</t>
+          <t>9959</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>5827</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>3106</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13215</t>
+          <t>14654</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5737</t>
+          <t>10450</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2361</t>
+          <t>4642</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11632</t>
+          <t>21333</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4351</t>
+          <t>5231</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1530</t>
+          <t>2329</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10462</t>
+          <t>10888</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>10087</t>
+          <t>15681</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4796</t>
+          <t>8925</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18990</t>
+          <t>27858</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>46341</t>
+          <t>53180</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>32246</t>
+          <t>37420</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>66950</t>
+          <t>73487</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>29927</t>
+          <t>34379</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14373</t>
+          <t>24548</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>46665</t>
+          <t>48373</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>76268</t>
+          <t>87559</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>48370</t>
+          <t>67338</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>101498</t>
+          <t>116014</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>207389</t>
+          <t>234561</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>180313</t>
+          <t>204024</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>238177</t>
+          <t>264838</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>149565</t>
+          <t>178924</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>68832</t>
+          <t>156774</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>204957</t>
+          <t>200310</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>356954</t>
+          <t>413485</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>233360</t>
+          <t>377167</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>424880</t>
+          <t>453651</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>28,32%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>438852</t>
+          <t>492885</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>408118</t>
+          <t>462854</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>469311</t>
+          <t>526243</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>743686</t>
+          <t>585510</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>676300</t>
+          <t>560392</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>843338</t>
+          <t>609840</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>72,5%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1182538</t>
+          <t>1078396</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1101195</t>
+          <t>1036138</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1336546</t>
+          <t>1115265</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>69,61%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>701643</t>
+          <t>794461</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>701643</t>
+          <t>794461</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>701643</t>
+          <t>794461</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>930032</t>
+          <t>807607</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>930032</t>
+          <t>807607</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>930032</t>
+          <t>807607</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1631675</t>
+          <t>1602068</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1631675</t>
+          <t>1602068</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1631675</t>
+          <t>1602068</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3248</t>
+          <t>3078</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>820</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>7710</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>4854</t>
+          <t>4784</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12062</t>
+          <t>11709</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>7861</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3844</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15796</t>
+          <t>15190</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>14186</t>
+          <t>13854</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7743</t>
+          <t>7731</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>24559</t>
+          <t>22682</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,22 +2919,22 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>5959</t>
+          <t>6043</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2749</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>12609</t>
+          <t>13402</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>20145</t>
+          <t>19897</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>12423</t>
+          <t>12398</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>31316</t>
+          <t>31984</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>50451</t>
+          <t>52836</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>36605</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>67777</t>
+          <t>69939</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>66405</t>
+          <t>68891</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>49707</t>
+          <t>55882</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>88194</t>
+          <t>85542</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>116856</t>
+          <t>121728</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>94588</t>
+          <t>99655</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>142827</t>
+          <t>146627</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>150213</t>
+          <t>173510</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>130201</t>
+          <t>145328</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>178609</t>
+          <t>200106</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>252119</t>
+          <t>204928</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>187112</t>
+          <t>178804</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>444823</t>
+          <t>225388</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>402332</t>
+          <t>378437</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>336261</t>
+          <t>343897</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>599651</t>
+          <t>416597</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>19,89%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>701382</t>
+          <t>739690</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>670846</t>
+          <t>710069</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>726703</t>
+          <t>769004</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>754801</t>
+          <t>827025</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>603841</t>
+          <t>802245</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>817199</t>
+          <t>856074</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1456183</t>
+          <t>1566715</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1282205</t>
+          <t>1527715</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1522311</t>
+          <t>1603725</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>74,8%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>72,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>76,56%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>919480</t>
+          <t>982968</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>919480</t>
+          <t>982968</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>919480</t>
+          <t>982968</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1084138</t>
+          <t>1111671</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1084138</t>
+          <t>1111671</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1084138</t>
+          <t>1111671</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2003618</t>
+          <t>2094639</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2003618</t>
+          <t>2094639</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2003618</t>
+          <t>2094639</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,102 +3453,102 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>12056</t>
+          <t>11380</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6292</t>
+          <t>5639</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>22745</t>
+          <t>21138</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>13719</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>7704</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>23139</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>25098</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>16415</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>37097</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
           <t>0,35%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>11948</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>6149</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>22130</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>24004</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>14807</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>36592</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>37186</t>
+          <t>42879</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>26297</t>
+          <t>31780</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>52037</t>
+          <t>57825</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,27 +3601,27 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>19952</t>
+          <t>21525</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>13296</t>
+          <t>14107</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>30634</t>
+          <t>31231</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>57137</t>
+          <t>64404</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>43826</t>
+          <t>49910</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>73593</t>
+          <t>80757</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>184619</t>
+          <t>210190</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>145680</t>
+          <t>179670</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>220376</t>
+          <t>243005</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>152932</t>
+          <t>168289</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>123261</t>
+          <t>146101</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>184498</t>
+          <t>195503</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>337550</t>
+          <t>378479</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>285418</t>
+          <t>340740</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>382375</t>
+          <t>421575</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>685652</t>
+          <t>772187</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>544855</t>
+          <t>718689</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>767920</t>
+          <t>828294</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>731326</t>
+          <t>744575</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>633279</t>
+          <t>701194</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>914965</t>
+          <t>788062</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1416978</t>
+          <t>1516762</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1242645</t>
+          <t>1446286</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1582515</t>
+          <t>1581154</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>21,93%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2514931</t>
+          <t>2461459</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2417162</t>
+          <t>2396453</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2711381</t>
+          <t>2523718</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2722349</t>
+          <t>2764944</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2572038</t>
+          <t>2713611</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2855380</t>
+          <t>2814299</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>5237280</t>
+          <t>5226403</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5079816</t>
+          <t>5151168</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5479821</t>
+          <t>5304047</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>71,43%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>73,55%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3434444</t>
+          <t>3498094</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3434444</t>
+          <t>3498094</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3434444</t>
+          <t>3498094</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3638506</t>
+          <t>3713052</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3638506</t>
+          <t>3713052</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3638506</t>
+          <t>3713052</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>7072950</t>
+          <t>7211146</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>7072950</t>
+          <t>7211146</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7072950</t>
+          <t>7211146</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
